--- a/Matano_etal_1985_a/Matano_etal_1985_a_Table1_snapshot.xlsx
+++ b/Matano_etal_1985_a/Matano_etal_1985_a_Table1_snapshot.xlsx
@@ -1,34 +1,274 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/Matano_etal_1985_a/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_C87705745A69B9536B1D93D1F4E098EAE5CD82A2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC8C2F7A-A4B8-CA42-A4B3-0EFEAA65D30B}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Table1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
+  <si>
+    <t>Table I. Body weights (BoW); volumes of total cerebellar nuclei (TCN), of medial (MCN), interpositus (ICN), and lateral (LCN) cerebellar nuclei; [Snapshot: body-weight and the four nuclear volume columns only; the size-index/ratio/percentage columns are derived and recomputed downstream.]</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Species</t>
+  </si>
+  <si>
+    <t>Specimens</t>
+  </si>
+  <si>
+    <t>Body weight BoW (g)</t>
+  </si>
+  <si>
+    <t>TCN volume (mm³)</t>
+  </si>
+  <si>
+    <t>MCN volume (mm³)</t>
+  </si>
+  <si>
+    <t>ICN volume (mm³)</t>
+  </si>
+  <si>
+    <t>LCN volume (mm³)</t>
+  </si>
+  <si>
+    <t>(1)</t>
+  </si>
+  <si>
+    <t>(2)</t>
+  </si>
+  <si>
+    <t>(3)</t>
+  </si>
+  <si>
+    <t>(4)</t>
+  </si>
+  <si>
+    <t>(5)</t>
+  </si>
+  <si>
+    <t>(6)</t>
+  </si>
+  <si>
+    <t>(7)</t>
+  </si>
+  <si>
+    <t>(8)</t>
+  </si>
+  <si>
+    <t>Insectivora</t>
+  </si>
+  <si>
+    <t>Suncus murinus</t>
+  </si>
+  <si>
+    <t>Tenrec ecaudatus</t>
+  </si>
+  <si>
+    <t>Setifer setosus</t>
+  </si>
+  <si>
+    <t>Hemicentetes semispin.</t>
+  </si>
+  <si>
+    <t>Echinops telfairi</t>
+  </si>
+  <si>
+    <t>Erinaceus europaeus</t>
+  </si>
+  <si>
+    <t>Sorex araneus</t>
+  </si>
+  <si>
+    <t>Sorex minutus</t>
+  </si>
+  <si>
+    <t>Crocidura flavescens</t>
+  </si>
+  <si>
+    <t>Crocidura r. russula</t>
+  </si>
+  <si>
+    <t>Scandentia</t>
+  </si>
+  <si>
+    <t>Tupaia glis</t>
+  </si>
+  <si>
+    <t>Urogale everetti</t>
+  </si>
+  <si>
+    <t>Prosimians</t>
+  </si>
+  <si>
+    <t>Microcebus murinus</t>
+  </si>
+  <si>
+    <t>Cheirogaleus major</t>
+  </si>
+  <si>
+    <t>Cheirogaleus medius</t>
+  </si>
+  <si>
+    <t>Lemur fulvus</t>
+  </si>
+  <si>
+    <t>Varecia variegata</t>
+  </si>
+  <si>
+    <t>Lepilemur ruficaudatus</t>
+  </si>
+  <si>
+    <t>Avahi l. laniger</t>
+  </si>
+  <si>
+    <t>Avahi l. occidentalis</t>
+  </si>
+  <si>
+    <t>Propithecus verreauxi</t>
+  </si>
+  <si>
+    <t>Daubentonia madagasc.</t>
+  </si>
+  <si>
+    <t>Loris tardigradus</t>
+  </si>
+  <si>
+    <t>Nycticebus coucang</t>
+  </si>
+  <si>
+    <t>Perodicticus potto</t>
+  </si>
+  <si>
+    <t>Galago senegalensis</t>
+  </si>
+  <si>
+    <t>Otolemur crassicaudatus</t>
+  </si>
+  <si>
+    <t>Galagoides demidoff</t>
+  </si>
+  <si>
+    <t>Tarsius spp.</t>
+  </si>
+  <si>
+    <t>Simians</t>
+  </si>
+  <si>
+    <t>Callithrix jacchus</t>
+  </si>
+  <si>
+    <t>Cebuella pygmaea</t>
+  </si>
+  <si>
+    <t>Saguinus midas</t>
+  </si>
+  <si>
+    <t>Saguinus oedipus</t>
+  </si>
+  <si>
+    <t>Cebus albifrons</t>
+  </si>
+  <si>
+    <t>Aotus trivirgatus</t>
+  </si>
+  <si>
+    <t>Callicebus moloch</t>
+  </si>
+  <si>
+    <t>Saimiri sciureus</t>
+  </si>
+  <si>
+    <t>Pithecia monachus</t>
+  </si>
+  <si>
+    <t>Alouatta seniculus</t>
+  </si>
+  <si>
+    <t>Ateles geoffroyi</t>
+  </si>
+  <si>
+    <t>Lagothrix lagothricha</t>
+  </si>
+  <si>
+    <t>Macaca mulatta</t>
+  </si>
+  <si>
+    <t>Cercocebus albigena</t>
+  </si>
+  <si>
+    <t>Papio anubis</t>
+  </si>
+  <si>
+    <t>Cercopithecus ascanius</t>
+  </si>
+  <si>
+    <t>Cercopithecus mitis</t>
+  </si>
+  <si>
+    <t>Miopithecus talapoin</t>
+  </si>
+  <si>
+    <t>Erythrocebus patas</t>
+  </si>
+  <si>
+    <t>Colobus badius</t>
+  </si>
+  <si>
+    <t>Pygathrix nemaeus</t>
+  </si>
+  <si>
+    <t>Nasalis larvatus</t>
+  </si>
+  <si>
+    <t>Hylobates lar</t>
+  </si>
+  <si>
+    <t>Pan troglodytes</t>
+  </si>
+  <si>
+    <t>Gorilla gorilla</t>
+  </si>
+  <si>
+    <t>Homo sapiens</t>
+  </si>
+  <si>
+    <t>Indri indri</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +287,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,1699 +589,1541 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H63"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Table I. Body weights (BoW); volumes of total cerebellar nuclei (TCN), of medial (MCN), interpositus (ICN), and lateral (LCN) cerebellar nuclei; [Snapshot: body-weight and the four nuclear volume columns only; the size-index/ratio/percentage columns are derived and recomputed downstream.]</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Species</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Specimens</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Body weight BoW (g)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>TCN volume (mm³)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>MCN volume (mm³)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>ICN volume (mm³)</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>LCN volume (mm³)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>(1)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>(2)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>(3)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>(4)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>(5)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>(6)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>(7)</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Insectivora</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5">
         <v>137</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Suncus murinus</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5">
         <v>1</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>33</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>1.06</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>0.23</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>0.38</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>0.44</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6">
         <v>577</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Tenrec ecaudatus</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6">
         <v>1</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>832</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>9.82</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>2.06</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>4.43</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>3.33</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7">
         <v>579</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Setifer setosus</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7">
         <v>1</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>248</v>
       </c>
-      <c r="E7" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="F7" t="n">
+      <c r="E7">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="F7">
         <v>1.2</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>1.78</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>1.21</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8">
         <v>581</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Hemicentetes semispin.</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8">
         <v>1</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>110</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>3.23</v>
       </c>
-      <c r="F8" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="F8">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G8">
         <v>1.52</v>
       </c>
-      <c r="H8" t="n">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
+      <c r="H8">
+        <v>1.1599999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9">
         <v>585</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Echinops telfairi</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9">
         <v>1</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>87.5</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>1.71</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>0.39</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>0.87</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>0.46</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10">
         <v>695</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Erinaceus europaeus</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10">
         <v>1</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>860</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>12.65</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>3.3</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>5.53</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>3.83</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11">
         <v>715</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Sorex araneus</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11">
         <v>1</v>
       </c>
-      <c r="D11" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="F11" t="n">
+      <c r="D11">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E11">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="F11">
         <v>0.18</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>0.18</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>0.21</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12">
         <v>769</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Sorex minutus</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12">
         <v>1</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>4.42</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>0.35</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>0.09</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>0.13</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>0.13</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13">
         <v>943</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Crocidura flavescens</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13">
         <v>1</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>33.1</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>1.17</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>0.27</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>0.42</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13">
         <v>0.47</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14">
         <v>1070</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Crocidura r. russula</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14">
         <v>1</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>11.1</v>
       </c>
-      <c r="E14" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="F14" t="n">
+      <c r="E14">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="F14">
         <v>0.12</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>0.23</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14">
         <v>0.23</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Scandentia</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16">
         <v>1263</v>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Tupaia glis</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" t="n">
+      <c r="B16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16">
         <v>170</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>12.46</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>3.93</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>3.4</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16">
         <v>5.13</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17">
         <v>1289</v>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Urogale everetti</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17">
         <v>1</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>275</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>15.07</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>4.13</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17">
         <v>3.94</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17">
         <v>7</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Prosimians</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19">
         <v>3199</v>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Microcebus murinus</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" t="n">
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
         <v>54</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19">
         <v>4.74</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19">
         <v>1.49</v>
       </c>
-      <c r="G19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="H19" t="n">
+      <c r="G19">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="H19">
         <v>2.11</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20">
         <v>3203</v>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Cheirogaleus major</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>2</v>
-      </c>
-      <c r="D20" t="n">
+      <c r="B20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20">
         <v>450</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20">
         <v>19.45</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20">
         <v>5.65</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20">
         <v>3.85</v>
       </c>
-      <c r="H20" t="n">
-        <v>9.949999999999999</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
+      <c r="H20">
+        <v>9.9499999999999993</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21">
         <v>3205</v>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Cheirogaleus medius</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
+      <c r="B21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21">
         <v>1</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>177</v>
       </c>
-      <c r="E21" t="n">
-        <v>9.449999999999999</v>
-      </c>
-      <c r="F21" t="n">
+      <c r="E21">
+        <v>9.4499999999999993</v>
+      </c>
+      <c r="F21">
         <v>3.24</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21">
         <v>1.94</v>
       </c>
-      <c r="H21" t="n">
-        <v>4.27</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
+      <c r="H21">
+        <v>4.2699999999999996</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22">
         <v>3215</v>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Lemur fulvus</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>2</v>
-      </c>
-      <c r="D22" t="n">
+      <c r="B22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22">
         <v>1400</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>86.28</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22">
         <v>26.65</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22">
         <v>27.58</v>
       </c>
-      <c r="H22" t="n">
-        <v>32.05</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
+      <c r="H22">
+        <v>32.049999999999997</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23">
         <v>3227</v>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Varecia variegata</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
+      <c r="B23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23">
         <v>1</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>3000</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23">
         <v>94.67</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23">
         <v>28.39</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23">
         <v>28.83</v>
       </c>
-      <c r="H23" t="n">
-        <v>37.45</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
+      <c r="H23">
+        <v>37.450000000000003</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24">
         <v>3239</v>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Lepilemur ruficaudatus</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
+      <c r="B24" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24">
         <v>1</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>915</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24">
         <v>23.07</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24">
         <v>7.31</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24">
         <v>6.41</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24">
         <v>9.35</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="n">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25">
         <v>3243</v>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Avahi l. laniger</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
+      <c r="B25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25">
         <v>1</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>1285</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>37.89</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25">
         <v>12.15</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25">
         <v>11.28</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H25">
         <v>14.46</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26">
         <v>3244</v>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Avahi l. occidentalis</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
+      <c r="B26" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26">
         <v>1</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>860</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26">
         <v>29.66</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26">
         <v>8.18</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26">
         <v>10.18</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H26">
         <v>11.3</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="n">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27">
         <v>3247</v>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Propithecus verreauxi</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>2</v>
-      </c>
-      <c r="D27" t="n">
+      <c r="B27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27">
         <v>3480</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27">
         <v>97.12</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27">
         <v>26.72</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27">
         <v>30.94</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H27">
         <v>39.46</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="n">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28">
         <v>3249</v>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>lndri indri</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>2</v>
-      </c>
-      <c r="D28" t="n">
+      <c r="B28" t="s">
+        <v>76</v>
+      </c>
+      <c r="C28">
+        <v>2</v>
+      </c>
+      <c r="D28">
         <v>6250</v>
       </c>
-      <c r="E28" t="n">
-        <v>141.3</v>
-      </c>
-      <c r="F28" t="n">
+      <c r="E28">
+        <v>141.30000000000001</v>
+      </c>
+      <c r="F28">
         <v>38.03</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28">
         <v>46.96</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H28">
         <v>56.31</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="n">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29">
         <v>3251</v>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Daubentonia madagasc.</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
+      <c r="B29" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29">
         <v>1</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29">
         <v>2800</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29">
         <v>126.08</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29">
         <v>28.94</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G29">
         <v>36.11</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H29">
         <v>61.03</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="n">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30">
         <v>3253</v>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Loris tardigradus</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>2</v>
-      </c>
-      <c r="D30" t="n">
+      <c r="B30" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="D30">
         <v>322</v>
       </c>
-      <c r="E30" t="n">
-        <v>17.99</v>
-      </c>
-      <c r="F30" t="n">
+      <c r="E30">
+        <v>17.989999999999998</v>
+      </c>
+      <c r="F30">
         <v>6.65</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G30">
         <v>5.58</v>
       </c>
-      <c r="H30" t="n">
+      <c r="H30">
         <v>5.76</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="n">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31">
         <v>3255</v>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Nycticebus coucang</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>2</v>
-      </c>
-      <c r="D31" t="n">
+      <c r="B31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31">
+        <v>2</v>
+      </c>
+      <c r="D31">
         <v>800</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31">
         <v>33.75</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31">
         <v>10.96</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G31">
         <v>8.76</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H31">
         <v>14.03</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="n">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32">
         <v>3259</v>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Perodicticus potto</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>2</v>
-      </c>
-      <c r="D32" t="n">
+      <c r="B32" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32">
+        <v>2</v>
+      </c>
+      <c r="D32">
         <v>1150</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32">
         <v>29.44</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F32">
         <v>8.76</v>
       </c>
-      <c r="G32" t="n">
+      <c r="G32">
         <v>8.43</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H32">
         <v>12.25</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="n">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33">
         <v>3265</v>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Galago senegalensis</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>2</v>
-      </c>
-      <c r="D33" t="n">
+      <c r="B33" t="s">
+        <v>45</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
+      </c>
+      <c r="D33">
         <v>186</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33">
         <v>12.6</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33">
         <v>4.43</v>
       </c>
-      <c r="G33" t="n">
+      <c r="G33">
         <v>3.77</v>
       </c>
-      <c r="H33" t="n">
-        <v>4.4</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
+      <c r="H33">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34">
         <v>3267</v>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Otolemur crassicaudatus</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>2</v>
-      </c>
-      <c r="D34" t="n">
+      <c r="B34" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34">
+        <v>2</v>
+      </c>
+      <c r="D34">
         <v>850</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34">
         <v>25.9</v>
       </c>
-      <c r="F34" t="n">
-        <v>9.630000000000001</v>
-      </c>
-      <c r="G34" t="n">
+      <c r="F34">
+        <v>9.6300000000000008</v>
+      </c>
+      <c r="G34">
         <v>6.63</v>
       </c>
-      <c r="H34" t="n">
-        <v>9.640000000000001</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
+      <c r="H34">
+        <v>9.64</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35">
         <v>3275</v>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Galagoides demidoff</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>2</v>
-      </c>
-      <c r="D35" t="n">
+      <c r="B35" t="s">
+        <v>47</v>
+      </c>
+      <c r="C35">
+        <v>2</v>
+      </c>
+      <c r="D35">
         <v>81</v>
       </c>
-      <c r="E35" t="n">
-        <v>8.220000000000001</v>
-      </c>
-      <c r="F35" t="n">
+      <c r="E35">
+        <v>8.2200000000000006</v>
+      </c>
+      <c r="F35">
         <v>3.08</v>
       </c>
-      <c r="G35" t="n">
+      <c r="G35">
         <v>2.08</v>
       </c>
-      <c r="H35" t="n">
+      <c r="H35">
         <v>3.06</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="n">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36">
         <v>3282</v>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Tarsius spp.</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
+      <c r="B36" t="s">
+        <v>48</v>
+      </c>
+      <c r="C36">
         <v>4</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36">
         <v>125</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36">
         <v>8.06</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F36">
         <v>2.87</v>
       </c>
-      <c r="G36" t="n">
+      <c r="G36">
         <v>1.82</v>
       </c>
-      <c r="H36" t="n">
+      <c r="H36">
         <v>3.37</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Simians</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38">
         <v>3287</v>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Callithrix jacchus</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>2</v>
-      </c>
-      <c r="D38" t="n">
+      <c r="B38" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38">
+        <v>2</v>
+      </c>
+      <c r="D38">
         <v>280</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38">
         <v>20.96</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F38">
         <v>7.59</v>
       </c>
-      <c r="G38" t="n">
+      <c r="G38">
         <v>5.44</v>
       </c>
-      <c r="H38" t="n">
+      <c r="H38">
         <v>7.93</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="n">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A39">
         <v>3289</v>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Cebuella pygmaea</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>2</v>
-      </c>
-      <c r="D39" t="n">
+      <c r="B39" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
+      <c r="D39">
         <v>120</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39">
         <v>11.48</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39">
         <v>3.93</v>
       </c>
-      <c r="G39" t="n">
+      <c r="G39">
         <v>3.2</v>
       </c>
-      <c r="H39" t="n">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
+      <c r="H39">
+        <v>4.3499999999999996</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40">
         <v>3305</v>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Saguinus midas</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>2</v>
-      </c>
-      <c r="D40" t="n">
+      <c r="B40" t="s">
+        <v>52</v>
+      </c>
+      <c r="C40">
+        <v>2</v>
+      </c>
+      <c r="D40">
         <v>340</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40">
         <v>21.57</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F40">
         <v>6.88</v>
       </c>
-      <c r="G40" t="n">
+      <c r="G40">
         <v>6.94</v>
       </c>
-      <c r="H40" t="n">
+      <c r="H40">
         <v>7.75</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="n">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A41">
         <v>3311</v>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Saguinus oedipus</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>2</v>
-      </c>
-      <c r="D41" t="n">
+      <c r="B41" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41">
+        <v>2</v>
+      </c>
+      <c r="D41">
         <v>380</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41">
         <v>24.6</v>
       </c>
-      <c r="F41" t="n">
-        <v>8.609999999999999</v>
-      </c>
-      <c r="G41" t="n">
+      <c r="F41">
+        <v>8.61</v>
+      </c>
+      <c r="G41">
         <v>7.19</v>
       </c>
-      <c r="H41" t="n">
-        <v>8.800000000000001</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
+      <c r="H41">
+        <v>8.8000000000000007</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A42">
         <v>3317</v>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Cebus albifrons</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
+      <c r="B42" t="s">
+        <v>54</v>
+      </c>
+      <c r="C42">
         <v>1</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42">
         <v>3100</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42">
         <v>173.18</v>
       </c>
-      <c r="F42" t="n">
+      <c r="F42">
         <v>34.68</v>
       </c>
-      <c r="G42" t="n">
-        <v>38.98</v>
-      </c>
-      <c r="H42" t="n">
+      <c r="G42">
+        <v>38.979999999999997</v>
+      </c>
+      <c r="H42">
         <v>99.52</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="n">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A43">
         <v>3325</v>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Aotus trivirgatus</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>2</v>
-      </c>
-      <c r="D43" t="n">
+      <c r="B43" t="s">
+        <v>55</v>
+      </c>
+      <c r="C43">
+        <v>2</v>
+      </c>
+      <c r="D43">
         <v>830</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43">
         <v>41.45</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43">
         <v>13.01</v>
       </c>
-      <c r="G43" t="n">
+      <c r="G43">
         <v>11.42</v>
       </c>
-      <c r="H43" t="n">
+      <c r="H43">
         <v>17.02</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="n">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A44">
         <v>3327</v>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Callicebus moloch</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>2</v>
-      </c>
-      <c r="D44" t="n">
+      <c r="B44" t="s">
+        <v>56</v>
+      </c>
+      <c r="C44">
+        <v>2</v>
+      </c>
+      <c r="D44">
         <v>900</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44">
         <v>61.41</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44">
         <v>20.7</v>
       </c>
-      <c r="G44" t="n">
+      <c r="G44">
         <v>19.47</v>
       </c>
-      <c r="H44" t="n">
+      <c r="H44">
         <v>21.24</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="n">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A45">
         <v>3335</v>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Saimiri sciureus</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>2</v>
-      </c>
-      <c r="D45" t="n">
+      <c r="B45" t="s">
+        <v>57</v>
+      </c>
+      <c r="C45">
+        <v>2</v>
+      </c>
+      <c r="D45">
         <v>660</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45">
         <v>73.22</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F45">
         <v>24.09</v>
       </c>
-      <c r="G45" t="n">
+      <c r="G45">
         <v>21.93</v>
       </c>
-      <c r="H45" t="n">
+      <c r="H45">
         <v>27.2</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="n">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A46">
         <v>3341</v>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Pithecia monachus</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>2</v>
-      </c>
-      <c r="D46" t="n">
+      <c r="B46" t="s">
+        <v>58</v>
+      </c>
+      <c r="C46">
+        <v>2</v>
+      </c>
+      <c r="D46">
         <v>1500</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E46">
         <v>109.36</v>
       </c>
-      <c r="F46" t="n">
+      <c r="F46">
         <v>23.91</v>
       </c>
-      <c r="G46" t="n">
+      <c r="G46">
         <v>31.78</v>
       </c>
-      <c r="H46" t="n">
+      <c r="H46">
         <v>53.67</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="n">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A47">
         <v>3363</v>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Alouatta seniculus</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>2</v>
-      </c>
-      <c r="D47" t="n">
+      <c r="B47" t="s">
+        <v>59</v>
+      </c>
+      <c r="C47">
+        <v>2</v>
+      </c>
+      <c r="D47">
         <v>6400</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47">
         <v>113.79</v>
       </c>
-      <c r="F47" t="n">
+      <c r="F47">
         <v>27.47</v>
       </c>
-      <c r="G47" t="n">
+      <c r="G47">
         <v>26.57</v>
       </c>
-      <c r="H47" t="n">
+      <c r="H47">
         <v>59.75</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="n">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A48">
         <v>3371</v>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Ateles geoffroyi</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
+      <c r="B48" t="s">
+        <v>60</v>
+      </c>
+      <c r="C48">
         <v>1</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D48">
         <v>8000</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48">
         <v>209.17</v>
       </c>
-      <c r="F48" t="n">
-        <v>34.63</v>
-      </c>
-      <c r="G48" t="n">
+      <c r="F48">
+        <v>34.630000000000003</v>
+      </c>
+      <c r="G48">
         <v>59.75</v>
       </c>
-      <c r="H48" t="n">
+      <c r="H48">
         <v>114.79</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="n">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A49">
         <v>3379</v>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Lagothrix lagothricha</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>2</v>
-      </c>
-      <c r="D49" t="n">
+      <c r="B49" t="s">
+        <v>61</v>
+      </c>
+      <c r="C49">
+        <v>2</v>
+      </c>
+      <c r="D49">
         <v>5200</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49">
         <v>212.95</v>
       </c>
-      <c r="F49" t="n">
+      <c r="F49">
         <v>44.15</v>
       </c>
-      <c r="G49" t="n">
+      <c r="G49">
         <v>60.23</v>
       </c>
-      <c r="H49" t="n">
+      <c r="H49">
         <v>108.57</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="n">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A50">
         <v>3391</v>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Macaca mulatta</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>2</v>
-      </c>
-      <c r="D50" t="n">
+      <c r="B50" t="s">
+        <v>62</v>
+      </c>
+      <c r="C50">
+        <v>2</v>
+      </c>
+      <c r="D50">
         <v>7800</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E50">
         <v>235.31</v>
       </c>
-      <c r="F50" t="n">
+      <c r="F50">
         <v>53.24</v>
       </c>
-      <c r="G50" t="n">
+      <c r="G50">
         <v>75.13</v>
       </c>
-      <c r="H50" t="n">
+      <c r="H50">
         <v>106.94</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="n">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A51">
         <v>3407</v>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Cercocebus albigena</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>2</v>
-      </c>
-      <c r="D51" t="n">
+      <c r="B51" t="s">
+        <v>63</v>
+      </c>
+      <c r="C51">
+        <v>2</v>
+      </c>
+      <c r="D51">
         <v>7900</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E51">
         <v>232.63</v>
       </c>
-      <c r="F51" t="n">
+      <c r="F51">
         <v>44.7</v>
       </c>
-      <c r="G51" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="H51" t="n">
+      <c r="G51">
+        <v>74.599999999999994</v>
+      </c>
+      <c r="H51">
         <v>113.33</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="n">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A52">
         <v>3415</v>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Papio anubis</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>2</v>
-      </c>
-      <c r="D52" t="n">
+      <c r="B52" t="s">
+        <v>64</v>
+      </c>
+      <c r="C52">
+        <v>2</v>
+      </c>
+      <c r="D52">
         <v>25000</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E52">
         <v>379.04</v>
       </c>
-      <c r="F52" t="n">
+      <c r="F52">
         <v>58.78</v>
       </c>
-      <c r="G52" t="n">
+      <c r="G52">
         <v>99.91</v>
       </c>
-      <c r="H52" t="n">
+      <c r="H52">
         <v>220.35</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="n">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A53">
         <v>3433</v>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Cercopithecus ascanius</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>2</v>
-      </c>
-      <c r="D53" t="n">
+      <c r="B53" t="s">
+        <v>65</v>
+      </c>
+      <c r="C53">
+        <v>2</v>
+      </c>
+      <c r="D53">
         <v>3400</v>
       </c>
-      <c r="E53" t="n">
-        <v>143.98</v>
-      </c>
-      <c r="F53" t="n">
+      <c r="E53">
+        <v>143.97999999999999</v>
+      </c>
+      <c r="F53">
         <v>34.61</v>
       </c>
-      <c r="G53" t="n">
+      <c r="G53">
         <v>41.7</v>
       </c>
-      <c r="H53" t="n">
+      <c r="H53">
         <v>67.67</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="n">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A54">
         <v>3453</v>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Cercopithecus mitis</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
+      <c r="B54" t="s">
+        <v>66</v>
+      </c>
+      <c r="C54">
         <v>1</v>
       </c>
-      <c r="D54" t="n">
+      <c r="D54">
         <v>6300</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E54">
         <v>171.16</v>
       </c>
-      <c r="F54" t="n">
-        <v>34.23</v>
-      </c>
-      <c r="G54" t="n">
+      <c r="F54">
+        <v>34.229999999999997</v>
+      </c>
+      <c r="G54">
         <v>54.55</v>
       </c>
-      <c r="H54" t="n">
+      <c r="H54">
         <v>82.38</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="n">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A55">
         <v>3469</v>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Miopithecus talapoin</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>2</v>
-      </c>
-      <c r="D55" t="n">
+      <c r="B55" t="s">
+        <v>67</v>
+      </c>
+      <c r="C55">
+        <v>2</v>
+      </c>
+      <c r="D55">
         <v>1200</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E55">
         <v>78.95</v>
       </c>
-      <c r="F55" t="n">
-        <v>18.69</v>
-      </c>
-      <c r="G55" t="n">
+      <c r="F55">
+        <v>18.690000000000001</v>
+      </c>
+      <c r="G55">
         <v>26.42</v>
       </c>
-      <c r="H55" t="n">
-        <v>33.84</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
+      <c r="H55">
+        <v>33.840000000000003</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A56">
         <v>3473</v>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Erythrocebus patas</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>2</v>
-      </c>
-      <c r="D56" t="n">
+      <c r="B56" t="s">
+        <v>68</v>
+      </c>
+      <c r="C56">
+        <v>2</v>
+      </c>
+      <c r="D56">
         <v>7800</v>
       </c>
-      <c r="E56" t="n">
-        <v>295.09</v>
-      </c>
-      <c r="F56" t="n">
-        <v>73.70999999999999</v>
-      </c>
-      <c r="G56" t="n">
-        <v>95.06999999999999</v>
-      </c>
-      <c r="H56" t="n">
+      <c r="E56">
+        <v>295.08999999999997</v>
+      </c>
+      <c r="F56">
+        <v>73.709999999999994</v>
+      </c>
+      <c r="G56">
+        <v>95.07</v>
+      </c>
+      <c r="H56">
         <v>126.31</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="n">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A57">
         <v>3477</v>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Colobus badius</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>2</v>
-      </c>
-      <c r="D57" t="n">
+      <c r="B57" t="s">
+        <v>69</v>
+      </c>
+      <c r="C57">
+        <v>2</v>
+      </c>
+      <c r="D57">
         <v>7000</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E57">
         <v>190.92</v>
       </c>
-      <c r="F57" t="n">
+      <c r="F57">
         <v>34.64</v>
       </c>
-      <c r="G57" t="n">
+      <c r="G57">
         <v>57.76</v>
       </c>
-      <c r="H57" t="n">
+      <c r="H57">
         <v>98.52</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="n">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A58">
         <v>3493</v>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Pygathrix nemaeus</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
+      <c r="B58" t="s">
+        <v>70</v>
+      </c>
+      <c r="C58">
         <v>1</v>
       </c>
-      <c r="D58" t="n">
+      <c r="D58">
         <v>7500</v>
       </c>
-      <c r="E58" t="n">
+      <c r="E58">
         <v>265.75</v>
       </c>
-      <c r="F58" t="n">
+      <c r="F58">
         <v>47.94</v>
       </c>
-      <c r="G58" t="n">
-        <v>80.76000000000001</v>
-      </c>
-      <c r="H58" t="n">
-        <v>137.05</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
+      <c r="G58">
+        <v>80.760000000000005</v>
+      </c>
+      <c r="H58">
+        <v>137.05000000000001</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A59">
         <v>3499</v>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Nasalis larvatus</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
+      <c r="B59" t="s">
+        <v>71</v>
+      </c>
+      <c r="C59">
         <v>1</v>
       </c>
-      <c r="D59" t="n">
+      <c r="D59">
         <v>14000</v>
       </c>
-      <c r="E59" t="n">
+      <c r="E59">
         <v>340.36</v>
       </c>
-      <c r="F59" t="n">
+      <c r="F59">
         <v>85.55</v>
       </c>
-      <c r="G59" t="n">
+      <c r="G59">
         <v>105.48</v>
       </c>
-      <c r="H59" t="n">
-        <v>149.33</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
+      <c r="H59">
+        <v>149.33000000000001</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A60">
         <v>3539</v>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Hylobates lar</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
+      <c r="B60" t="s">
+        <v>72</v>
+      </c>
+      <c r="C60">
         <v>1</v>
       </c>
-      <c r="D60" t="n">
+      <c r="D60">
         <v>5700</v>
       </c>
-      <c r="E60" t="n">
+      <c r="E60">
         <v>242.09</v>
       </c>
-      <c r="F60" t="n">
-        <v>35.41</v>
-      </c>
-      <c r="G60" t="n">
-        <v>65.59999999999999</v>
-      </c>
-      <c r="H60" t="n">
-        <v>141.08</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
+      <c r="F60">
+        <v>35.409999999999997</v>
+      </c>
+      <c r="G60">
+        <v>65.599999999999994</v>
+      </c>
+      <c r="H60">
+        <v>141.08000000000001</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A61">
         <v>3549</v>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Pan troglodytes</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
+      <c r="B61" t="s">
+        <v>73</v>
+      </c>
+      <c r="C61">
         <v>1</v>
       </c>
-      <c r="D61" t="n">
+      <c r="D61">
         <v>46000</v>
       </c>
-      <c r="E61" t="n">
-        <v>601.42</v>
-      </c>
-      <c r="F61" t="n">
+      <c r="E61">
+        <v>601.41999999999996</v>
+      </c>
+      <c r="F61">
         <v>58.32</v>
       </c>
-      <c r="G61" t="n">
+      <c r="G61">
         <v>87.27</v>
       </c>
-      <c r="H61" t="n">
+      <c r="H61">
         <v>455.83</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="n">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A62">
         <v>3551</v>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Gorilla gorilla</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>2</v>
-      </c>
-      <c r="D62" t="n">
+      <c r="B62" t="s">
+        <v>74</v>
+      </c>
+      <c r="C62">
+        <v>2</v>
+      </c>
+      <c r="D62">
         <v>105000</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E62">
         <v>740.4</v>
       </c>
-      <c r="F62" t="n">
+      <c r="F62">
         <v>93.44</v>
       </c>
-      <c r="G62" t="n">
+      <c r="G62">
         <v>112.36</v>
       </c>
-      <c r="H62" t="n">
+      <c r="H62">
         <v>534.6</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="n">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A63">
         <v>3553</v>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Homo sapiens</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>2</v>
-      </c>
-      <c r="D63" t="n">
+      <c r="B63" t="s">
+        <v>75</v>
+      </c>
+      <c r="C63">
+        <v>2</v>
+      </c>
+      <c r="D63">
         <v>65000</v>
       </c>
-      <c r="E63" t="n">
+      <c r="E63">
         <v>1513.78</v>
       </c>
-      <c r="F63" t="n">
+      <c r="F63">
         <v>156.4</v>
       </c>
-      <c r="G63" t="n">
+      <c r="G63">
         <v>190.48</v>
       </c>
-      <c r="H63" t="n">
-        <v>1166.9</v>
+      <c r="H63">
+        <v>1166.9000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2109,6 +2132,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
@@ -2363,34 +2406,46 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18C6ECD5-2CA1-405C-B556-5759FDCDBA6A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E73D3026-E0BF-4D0A-BEE2-CD2EF4FC2A98}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2678CC6C-E03B-4150-AD9B-3423ACE206CC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2678CC6C-E03B-4150-AD9B-3423ACE206CC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E73D3026-E0BF-4D0A-BEE2-CD2EF4FC2A98}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18C6ECD5-2CA1-405C-B556-5759FDCDBA6A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>